--- a/data/trans_orig/P1406-Habitat-trans_orig.xlsx
+++ b/data/trans_orig/P1406-Habitat-trans_orig.xlsx
@@ -536,7 +536,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Población con diagnóstico de úlcera de estómago en 2012</t>
+          <t>Población con diagnóstico de úlcera de estómago en 2012 (tasa de respuesta: 99,95%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -731,12 +731,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>1870</t>
+          <t>1890</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>12445</t>
+          <t>10610</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -751,7 +751,7 @@
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>1,77%</t>
+          <t>1,51%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -766,12 +766,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>4063</t>
+          <t>4197</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>16866</t>
+          <t>17403</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -781,12 +781,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>0,58%</t>
+          <t>0,6%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>2,42%</t>
+          <t>2,5%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -801,12 +801,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>7462</t>
+          <t>7824</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>22673</t>
+          <t>22642</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -816,7 +816,7 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>0,53%</t>
+          <t>0,56%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
@@ -844,12 +844,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>691024</t>
+          <t>692859</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>701599</t>
+          <t>701579</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -859,7 +859,7 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>98,23%</t>
+          <t>98,49%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
@@ -879,12 +879,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>680184</t>
+          <t>679647</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>692987</t>
+          <t>692853</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -894,12 +894,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>97,58%</t>
+          <t>97,5%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>99,42%</t>
+          <t>99,4%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -914,12 +914,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>1377846</t>
+          <t>1377877</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>1393057</t>
+          <t>1392695</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -934,7 +934,7 @@
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>99,47%</t>
+          <t>99,44%</t>
         </is>
       </c>
     </row>
@@ -1074,12 +1074,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>7490</t>
+          <t>6689</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>22421</t>
+          <t>21304</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -1089,12 +1089,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>0,74%</t>
+          <t>0,66%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>2,2%</t>
+          <t>2,09%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -1109,12 +1109,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>7314</t>
+          <t>6528</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>23293</t>
+          <t>22558</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -1124,12 +1124,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>0,71%</t>
+          <t>0,64%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>2,27%</t>
+          <t>2,19%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -1144,12 +1144,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>17940</t>
+          <t>17166</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>38719</t>
+          <t>37842</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -1159,12 +1159,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>0,88%</t>
+          <t>0,84%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>1,89%</t>
+          <t>1,85%</t>
         </is>
       </c>
     </row>
@@ -1187,12 +1187,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>995526</t>
+          <t>996643</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>1010457</t>
+          <t>1011258</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -1202,12 +1202,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>97,8%</t>
+          <t>97,91%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>99,26%</t>
+          <t>99,34%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -1222,12 +1222,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>1004498</t>
+          <t>1005233</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>1020477</t>
+          <t>1021263</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -1237,12 +1237,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>97,73%</t>
+          <t>97,81%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>99,29%</t>
+          <t>99,36%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -1257,12 +1257,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>2007019</t>
+          <t>2007896</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>2027798</t>
+          <t>2028572</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -1272,12 +1272,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>98,11%</t>
+          <t>98,15%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>99,12%</t>
+          <t>99,16%</t>
         </is>
       </c>
     </row>
@@ -1417,12 +1417,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>6273</t>
+          <t>6240</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>19246</t>
+          <t>19075</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -1432,12 +1432,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>0,83%</t>
+          <t>0,82%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>2,54%</t>
+          <t>2,52%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -1452,12 +1452,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>3189</t>
+          <t>4040</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>16914</t>
+          <t>16622</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -1467,12 +1467,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>0,41%</t>
+          <t>0,52%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>2,18%</t>
+          <t>2,14%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -1487,12 +1487,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>11669</t>
+          <t>11965</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>31785</t>
+          <t>31128</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -1502,12 +1502,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>0,76%</t>
+          <t>0,78%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>2,07%</t>
+          <t>2,03%</t>
         </is>
       </c>
     </row>
@@ -1530,12 +1530,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>738377</t>
+          <t>738548</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>751350</t>
+          <t>751383</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -1545,12 +1545,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>97,46%</t>
+          <t>97,48%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>99,17%</t>
+          <t>99,18%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -1565,12 +1565,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>760260</t>
+          <t>760552</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>773985</t>
+          <t>773134</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -1580,12 +1580,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>97,82%</t>
+          <t>97,86%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>99,59%</t>
+          <t>99,48%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -1600,12 +1600,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>1503012</t>
+          <t>1503669</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>1523128</t>
+          <t>1522832</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -1615,12 +1615,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>97,93%</t>
+          <t>97,97%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>99,24%</t>
+          <t>99,22%</t>
         </is>
       </c>
     </row>
@@ -1760,12 +1760,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>5871</t>
+          <t>5001</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>20329</t>
+          <t>19590</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -1775,12 +1775,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>0,62%</t>
+          <t>0,53%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>2,15%</t>
+          <t>2,07%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -1795,12 +1795,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>7165</t>
+          <t>7175</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>23074</t>
+          <t>22998</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -1830,12 +1830,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>15602</t>
+          <t>15692</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>36822</t>
+          <t>37380</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -1850,7 +1850,7 @@
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>1,84%</t>
+          <t>1,87%</t>
         </is>
       </c>
     </row>
@@ -1873,12 +1873,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>927410</t>
+          <t>928149</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>941868</t>
+          <t>942738</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -1888,12 +1888,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>97,85%</t>
+          <t>97,93%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>99,38%</t>
+          <t>99,47%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -1908,12 +1908,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>1028827</t>
+          <t>1028903</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>1044736</t>
+          <t>1044726</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -1943,12 +1943,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>1962818</t>
+          <t>1962260</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>1984038</t>
+          <t>1983948</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -1958,7 +1958,7 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>98,16%</t>
+          <t>98,13%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
@@ -2103,12 +2103,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>29268</t>
+          <t>29682</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>54677</t>
+          <t>54985</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -2118,7 +2118,7 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>0,85%</t>
+          <t>0,87%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
@@ -2138,12 +2138,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>31075</t>
+          <t>30711</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>57787</t>
+          <t>57239</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -2153,12 +2153,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>0,87%</t>
+          <t>0,86%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>1,63%</t>
+          <t>1,61%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -2173,12 +2173,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>65841</t>
+          <t>67000</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>103391</t>
+          <t>104777</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -2188,12 +2188,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>0,94%</t>
+          <t>0,96%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>1,48%</t>
+          <t>1,5%</t>
         </is>
       </c>
     </row>
@@ -2216,12 +2216,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>3372102</t>
+          <t>3371794</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>3397511</t>
+          <t>3397097</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -2236,7 +2236,7 @@
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>99,15%</t>
+          <t>99,13%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -2251,12 +2251,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>3496129</t>
+          <t>3496677</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>3522841</t>
+          <t>3523205</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -2266,12 +2266,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>98,37%</t>
+          <t>98,39%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>99,13%</t>
+          <t>99,14%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -2286,12 +2286,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>6877303</t>
+          <t>6875917</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>6914853</t>
+          <t>6913694</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -2301,12 +2301,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>98,52%</t>
+          <t>98,5%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>99,06%</t>
+          <t>99,04%</t>
         </is>
       </c>
     </row>
@@ -2483,7 +2483,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Población con diagnóstico de úlcera de estómago en 2016</t>
+          <t>Población con diagnóstico de úlcera de estómago en 2016 (tasa de respuesta: 100,0%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -2678,12 +2678,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>1029</t>
+          <t>1042</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>9929</t>
+          <t>9412</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -2698,7 +2698,7 @@
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>1,47%</t>
+          <t>1,39%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -2713,12 +2713,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>2081</t>
+          <t>1992</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>12520</t>
+          <t>12027</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -2728,12 +2728,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>0,31%</t>
+          <t>0,3%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>1,86%</t>
+          <t>1,79%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -2748,12 +2748,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>5025</t>
+          <t>4081</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>17156</t>
+          <t>17359</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -2763,12 +2763,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>0,37%</t>
+          <t>0,3%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>1,27%</t>
+          <t>1,29%</t>
         </is>
       </c>
     </row>
@@ -2791,12 +2791,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>664871</t>
+          <t>665388</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>673771</t>
+          <t>673758</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -2806,7 +2806,7 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>98,53%</t>
+          <t>98,61%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
@@ -2826,12 +2826,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>660319</t>
+          <t>660812</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>670758</t>
+          <t>670847</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -2841,12 +2841,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>98,14%</t>
+          <t>98,21%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>99,69%</t>
+          <t>99,7%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -2861,12 +2861,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>1330483</t>
+          <t>1330280</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>1342614</t>
+          <t>1343558</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -2876,12 +2876,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>98,73%</t>
+          <t>98,71%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>99,63%</t>
+          <t>99,7%</t>
         </is>
       </c>
     </row>
@@ -3021,12 +3021,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>2177</t>
+          <t>2125</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>15677</t>
+          <t>13909</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -3041,7 +3041,7 @@
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>1,53%</t>
+          <t>1,36%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -3056,12 +3056,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>4582</t>
+          <t>4385</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>19328</t>
+          <t>18145</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -3071,12 +3071,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>0,44%</t>
+          <t>0,42%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>1,85%</t>
+          <t>1,74%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -3091,12 +3091,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>8991</t>
+          <t>8753</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>27211</t>
+          <t>26795</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -3106,12 +3106,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>0,44%</t>
+          <t>0,42%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>1,32%</t>
+          <t>1,3%</t>
         </is>
       </c>
     </row>
@@ -3134,12 +3134,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>1006754</t>
+          <t>1008522</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>1020254</t>
+          <t>1020306</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -3149,7 +3149,7 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>98,47%</t>
+          <t>98,64%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
@@ -3169,12 +3169,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>1023585</t>
+          <t>1024768</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>1038331</t>
+          <t>1038528</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -3184,12 +3184,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>98,15%</t>
+          <t>98,26%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>99,56%</t>
+          <t>99,58%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -3204,12 +3204,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>2038133</t>
+          <t>2038549</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>2056353</t>
+          <t>2056591</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -3219,12 +3219,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>98,68%</t>
+          <t>98,7%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>99,56%</t>
+          <t>99,58%</t>
         </is>
       </c>
     </row>
@@ -3369,7 +3369,7 @@
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>7057</t>
+          <t>6026</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -3384,7 +3384,7 @@
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>0,93%</t>
+          <t>0,79%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -3399,12 +3399,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>3378</t>
+          <t>3183</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>16272</t>
+          <t>14747</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -3414,12 +3414,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>0,43%</t>
+          <t>0,41%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>2,07%</t>
+          <t>1,88%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -3434,12 +3434,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>4734</t>
+          <t>4826</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>18898</t>
+          <t>18874</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -3477,7 +3477,7 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>752495</t>
+          <t>753526</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
@@ -3492,7 +3492,7 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>99,07%</t>
+          <t>99,21%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
@@ -3512,12 +3512,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>768739</t>
+          <t>770264</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>781633</t>
+          <t>781828</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -3527,12 +3527,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>97,93%</t>
+          <t>98,12%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>99,57%</t>
+          <t>99,59%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -3547,12 +3547,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>1525665</t>
+          <t>1525689</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>1539829</t>
+          <t>1539737</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -3707,12 +3707,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>893</t>
+          <t>899</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>7867</t>
+          <t>8612</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -3727,7 +3727,7 @@
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>0,84%</t>
+          <t>0,92%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -3742,12 +3742,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>4600</t>
+          <t>4714</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>18559</t>
+          <t>18560</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -3757,7 +3757,7 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>0,44%</t>
+          <t>0,45%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
@@ -3777,12 +3777,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>6760</t>
+          <t>7443</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>22580</t>
+          <t>22096</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -3792,12 +3792,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>0,34%</t>
+          <t>0,38%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>1,14%</t>
+          <t>1,12%</t>
         </is>
       </c>
     </row>
@@ -3820,12 +3820,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>929700</t>
+          <t>928955</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>936674</t>
+          <t>936668</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -3835,7 +3835,7 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>99,16%</t>
+          <t>99,08%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
@@ -3855,12 +3855,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>1025220</t>
+          <t>1025219</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>1039179</t>
+          <t>1039065</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -3875,7 +3875,7 @@
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>99,56%</t>
+          <t>99,55%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -3890,12 +3890,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>1958766</t>
+          <t>1959250</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>1974586</t>
+          <t>1973903</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -3905,12 +3905,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>98,86%</t>
+          <t>98,88%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>99,66%</t>
+          <t>99,62%</t>
         </is>
       </c>
     </row>
@@ -4050,12 +4050,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>8161</t>
+          <t>8495</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>24787</t>
+          <t>25606</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -4065,12 +4065,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>0,24%</t>
+          <t>0,25%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>0,73%</t>
+          <t>0,75%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -4085,12 +4085,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>23999</t>
+          <t>23683</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>46915</t>
+          <t>48825</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -4100,12 +4100,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>0,68%</t>
+          <t>0,67%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>1,32%</t>
+          <t>1,38%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -4120,12 +4120,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>35217</t>
+          <t>37159</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>65188</t>
+          <t>67854</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -4135,12 +4135,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>0,51%</t>
+          <t>0,54%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>0,94%</t>
+          <t>0,98%</t>
         </is>
       </c>
     </row>
@@ -4163,12 +4163,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>3369563</t>
+          <t>3368744</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>3386189</t>
+          <t>3385855</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -4178,12 +4178,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>99,27%</t>
+          <t>99,25%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>99,76%</t>
+          <t>99,75%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -4198,12 +4198,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>3497627</t>
+          <t>3495717</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>3520543</t>
+          <t>3520859</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -4213,12 +4213,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>98,68%</t>
+          <t>98,62%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>99,32%</t>
+          <t>99,33%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -4233,12 +4233,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>6873704</t>
+          <t>6871038</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>6903675</t>
+          <t>6901733</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -4248,12 +4248,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>99,06%</t>
+          <t>99,02%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>99,49%</t>
+          <t>99,46%</t>
         </is>
       </c>
     </row>

--- a/data/trans_orig/P1406-Habitat-trans_orig.xlsx
+++ b/data/trans_orig/P1406-Habitat-trans_orig.xlsx
@@ -731,12 +731,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>1890</t>
+          <t>1865</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>10610</t>
+          <t>11093</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -751,7 +751,7 @@
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>1,51%</t>
+          <t>1,58%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -766,12 +766,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>4197</t>
+          <t>3373</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>17403</t>
+          <t>16306</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -781,12 +781,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>0,6%</t>
+          <t>0,48%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>2,5%</t>
+          <t>2,34%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -801,12 +801,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>7824</t>
+          <t>7075</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>22642</t>
+          <t>22116</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -816,12 +816,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>0,56%</t>
+          <t>0,51%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>1,62%</t>
+          <t>1,58%</t>
         </is>
       </c>
     </row>
@@ -844,12 +844,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>692859</t>
+          <t>692376</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>701579</t>
+          <t>701604</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -859,7 +859,7 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>98,49%</t>
+          <t>98,42%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
@@ -879,12 +879,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>679647</t>
+          <t>680744</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>692853</t>
+          <t>693677</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -894,12 +894,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>97,5%</t>
+          <t>97,66%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>99,4%</t>
+          <t>99,52%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -914,12 +914,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>1377877</t>
+          <t>1378403</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>1392695</t>
+          <t>1393444</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -929,12 +929,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>98,38%</t>
+          <t>98,42%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>99,44%</t>
+          <t>99,49%</t>
         </is>
       </c>
     </row>
@@ -1074,12 +1074,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>6689</t>
+          <t>7486</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>21304</t>
+          <t>21890</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -1089,12 +1089,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>0,66%</t>
+          <t>0,74%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>2,09%</t>
+          <t>2,15%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -1109,12 +1109,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>6528</t>
+          <t>7429</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>22558</t>
+          <t>22022</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -1124,12 +1124,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>0,64%</t>
+          <t>0,72%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>2,19%</t>
+          <t>2,14%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -1144,12 +1144,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>17166</t>
+          <t>17151</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>37842</t>
+          <t>38247</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -1164,7 +1164,7 @@
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>1,85%</t>
+          <t>1,87%</t>
         </is>
       </c>
     </row>
@@ -1187,12 +1187,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>996643</t>
+          <t>996057</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>1011258</t>
+          <t>1010461</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -1202,12 +1202,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>97,91%</t>
+          <t>97,85%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>99,34%</t>
+          <t>99,26%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -1222,12 +1222,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>1005233</t>
+          <t>1005769</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>1021263</t>
+          <t>1020362</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -1237,12 +1237,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>97,81%</t>
+          <t>97,86%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>99,36%</t>
+          <t>99,28%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -1257,12 +1257,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>2007896</t>
+          <t>2007491</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>2028572</t>
+          <t>2028587</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -1272,7 +1272,7 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>98,15%</t>
+          <t>98,13%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
@@ -1417,12 +1417,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>6240</t>
+          <t>6359</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>19075</t>
+          <t>20072</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -1432,12 +1432,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>0,82%</t>
+          <t>0,84%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>2,52%</t>
+          <t>2,65%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -1452,12 +1452,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>4040</t>
+          <t>3168</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>16622</t>
+          <t>17507</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -1467,12 +1467,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>0,52%</t>
+          <t>0,41%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>2,14%</t>
+          <t>2,25%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -1487,12 +1487,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>11965</t>
+          <t>12444</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>31128</t>
+          <t>31724</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -1502,12 +1502,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>0,78%</t>
+          <t>0,81%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>2,03%</t>
+          <t>2,07%</t>
         </is>
       </c>
     </row>
@@ -1530,12 +1530,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>738548</t>
+          <t>737551</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>751383</t>
+          <t>751264</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -1545,12 +1545,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>97,48%</t>
+          <t>97,35%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>99,18%</t>
+          <t>99,16%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -1565,12 +1565,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>760552</t>
+          <t>759667</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>773134</t>
+          <t>774006</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -1580,12 +1580,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>97,86%</t>
+          <t>97,75%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>99,48%</t>
+          <t>99,59%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -1600,12 +1600,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>1503669</t>
+          <t>1503073</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>1522832</t>
+          <t>1522353</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -1615,12 +1615,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>97,97%</t>
+          <t>97,93%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>99,22%</t>
+          <t>99,19%</t>
         </is>
       </c>
     </row>
@@ -1760,12 +1760,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>5001</t>
+          <t>5126</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>19590</t>
+          <t>21026</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -1775,12 +1775,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>0,53%</t>
+          <t>0,54%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>2,07%</t>
+          <t>2,22%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -1795,12 +1795,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>7175</t>
+          <t>6885</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>22998</t>
+          <t>22969</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -1810,12 +1810,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>0,68%</t>
+          <t>0,65%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>2,19%</t>
+          <t>2,18%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -1830,12 +1830,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>15692</t>
+          <t>15471</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>37380</t>
+          <t>37119</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -1845,12 +1845,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>0,78%</t>
+          <t>0,77%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>1,87%</t>
+          <t>1,86%</t>
         </is>
       </c>
     </row>
@@ -1873,12 +1873,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>928149</t>
+          <t>926713</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>942738</t>
+          <t>942613</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -1888,12 +1888,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>97,93%</t>
+          <t>97,78%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>99,47%</t>
+          <t>99,46%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -1908,12 +1908,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>1028903</t>
+          <t>1028932</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>1044726</t>
+          <t>1045016</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -1923,12 +1923,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>97,81%</t>
+          <t>97,82%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>99,32%</t>
+          <t>99,35%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -1943,12 +1943,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>1962260</t>
+          <t>1962521</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>1983948</t>
+          <t>1984169</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -1958,12 +1958,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>98,13%</t>
+          <t>98,14%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>99,22%</t>
+          <t>99,23%</t>
         </is>
       </c>
     </row>
@@ -2103,12 +2103,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>29682</t>
+          <t>28429</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>54985</t>
+          <t>55170</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -2118,12 +2118,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>0,87%</t>
+          <t>0,83%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>1,6%</t>
+          <t>1,61%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -2138,12 +2138,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>30711</t>
+          <t>31371</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>57239</t>
+          <t>57835</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -2153,12 +2153,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>0,86%</t>
+          <t>0,88%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>1,61%</t>
+          <t>1,63%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -2173,12 +2173,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>67000</t>
+          <t>65962</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>104777</t>
+          <t>104166</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -2188,12 +2188,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>0,96%</t>
+          <t>0,94%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>1,5%</t>
+          <t>1,49%</t>
         </is>
       </c>
     </row>
@@ -2216,12 +2216,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>3371794</t>
+          <t>3371609</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>3397097</t>
+          <t>3398350</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -2231,12 +2231,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>98,4%</t>
+          <t>98,39%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>99,13%</t>
+          <t>99,17%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -2251,12 +2251,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>3496677</t>
+          <t>3496081</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>3523205</t>
+          <t>3522545</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -2266,12 +2266,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>98,39%</t>
+          <t>98,37%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>99,14%</t>
+          <t>99,12%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -2286,12 +2286,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>6875917</t>
+          <t>6876528</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>6913694</t>
+          <t>6914732</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -2301,12 +2301,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>98,5%</t>
+          <t>98,51%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>99,04%</t>
+          <t>99,06%</t>
         </is>
       </c>
     </row>
@@ -2678,12 +2678,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>1042</t>
+          <t>1029</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>9412</t>
+          <t>9937</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -2698,7 +2698,7 @@
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>1,39%</t>
+          <t>1,47%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -2713,12 +2713,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>1992</t>
+          <t>2055</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>12027</t>
+          <t>12874</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -2728,12 +2728,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>0,3%</t>
+          <t>0,31%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>1,79%</t>
+          <t>1,91%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -2748,12 +2748,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>4081</t>
+          <t>4841</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>17359</t>
+          <t>17145</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -2763,12 +2763,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>0,3%</t>
+          <t>0,36%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>1,29%</t>
+          <t>1,27%</t>
         </is>
       </c>
     </row>
@@ -2791,12 +2791,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>665388</t>
+          <t>664863</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>673758</t>
+          <t>673771</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -2806,7 +2806,7 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>98,61%</t>
+          <t>98,53%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
@@ -2826,12 +2826,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>660812</t>
+          <t>659965</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>670847</t>
+          <t>670784</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -2841,12 +2841,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>98,21%</t>
+          <t>98,09%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>99,7%</t>
+          <t>99,69%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -2861,12 +2861,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>1330280</t>
+          <t>1330494</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>1343558</t>
+          <t>1342798</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -2876,12 +2876,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>98,71%</t>
+          <t>98,73%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>99,7%</t>
+          <t>99,64%</t>
         </is>
       </c>
     </row>
@@ -3021,12 +3021,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>2125</t>
+          <t>2171</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>13909</t>
+          <t>14286</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -3041,7 +3041,7 @@
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>1,36%</t>
+          <t>1,4%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -3056,12 +3056,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>4385</t>
+          <t>5347</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>18145</t>
+          <t>20193</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -3071,12 +3071,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>0,42%</t>
+          <t>0,51%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>1,74%</t>
+          <t>1,94%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -3091,12 +3091,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>8753</t>
+          <t>9313</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>26795</t>
+          <t>26557</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -3106,12 +3106,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>0,42%</t>
+          <t>0,45%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>1,3%</t>
+          <t>1,29%</t>
         </is>
       </c>
     </row>
@@ -3134,12 +3134,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>1008522</t>
+          <t>1008145</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>1020306</t>
+          <t>1020260</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -3149,7 +3149,7 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>98,64%</t>
+          <t>98,6%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
@@ -3169,12 +3169,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>1024768</t>
+          <t>1022720</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>1038528</t>
+          <t>1037566</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -3184,12 +3184,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>98,26%</t>
+          <t>98,06%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>99,58%</t>
+          <t>99,49%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -3204,12 +3204,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>2038549</t>
+          <t>2038787</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>2056591</t>
+          <t>2056031</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -3219,12 +3219,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>98,7%</t>
+          <t>98,71%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>99,58%</t>
+          <t>99,55%</t>
         </is>
       </c>
     </row>
@@ -3369,7 +3369,7 @@
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>6026</t>
+          <t>7572</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -3384,7 +3384,7 @@
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>0,79%</t>
+          <t>1,0%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -3399,12 +3399,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>3183</t>
+          <t>3218</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>14747</t>
+          <t>15765</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -3419,7 +3419,7 @@
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>1,88%</t>
+          <t>2,01%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -3434,12 +3434,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>4826</t>
+          <t>4947</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>18874</t>
+          <t>18027</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -3449,12 +3449,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>0,31%</t>
+          <t>0,32%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>1,22%</t>
+          <t>1,17%</t>
         </is>
       </c>
     </row>
@@ -3477,7 +3477,7 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>753526</t>
+          <t>751980</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
@@ -3492,7 +3492,7 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>99,21%</t>
+          <t>99,0%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
@@ -3512,12 +3512,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>770264</t>
+          <t>769246</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>781828</t>
+          <t>781793</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -3527,7 +3527,7 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>98,12%</t>
+          <t>97,99%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
@@ -3547,12 +3547,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>1525689</t>
+          <t>1526536</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>1539737</t>
+          <t>1539616</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -3562,12 +3562,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>98,78%</t>
+          <t>98,83%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>99,69%</t>
+          <t>99,68%</t>
         </is>
       </c>
     </row>
@@ -3707,12 +3707,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>899</t>
+          <t>902</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>8612</t>
+          <t>8386</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -3727,7 +3727,7 @@
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>0,92%</t>
+          <t>0,89%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -3742,12 +3742,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>4714</t>
+          <t>4663</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>18560</t>
+          <t>19079</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -3762,7 +3762,7 @@
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>1,78%</t>
+          <t>1,83%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -3777,12 +3777,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>7443</t>
+          <t>7212</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>22096</t>
+          <t>21802</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -3792,12 +3792,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>0,38%</t>
+          <t>0,36%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>1,12%</t>
+          <t>1,1%</t>
         </is>
       </c>
     </row>
@@ -3820,12 +3820,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>928955</t>
+          <t>929181</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>936668</t>
+          <t>936665</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -3835,7 +3835,7 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>99,08%</t>
+          <t>99,11%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
@@ -3855,12 +3855,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>1025219</t>
+          <t>1024700</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>1039065</t>
+          <t>1039116</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -3870,7 +3870,7 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>98,22%</t>
+          <t>98,17%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
@@ -3890,12 +3890,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>1959250</t>
+          <t>1959544</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>1973903</t>
+          <t>1974134</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -3905,12 +3905,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>98,88%</t>
+          <t>98,9%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>99,62%</t>
+          <t>99,64%</t>
         </is>
       </c>
     </row>
@@ -4050,12 +4050,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>8495</t>
+          <t>8735</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>25606</t>
+          <t>25624</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -4065,7 +4065,7 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>0,25%</t>
+          <t>0,26%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
@@ -4085,12 +4085,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>23683</t>
+          <t>23505</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>48825</t>
+          <t>47876</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -4100,12 +4100,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>0,67%</t>
+          <t>0,66%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>1,38%</t>
+          <t>1,35%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -4120,12 +4120,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>37159</t>
+          <t>36835</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>67854</t>
+          <t>66705</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -4135,12 +4135,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>0,54%</t>
+          <t>0,53%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>0,98%</t>
+          <t>0,96%</t>
         </is>
       </c>
     </row>
@@ -4163,12 +4163,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>3368744</t>
+          <t>3368726</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>3385855</t>
+          <t>3385615</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -4183,7 +4183,7 @@
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>99,75%</t>
+          <t>99,74%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -4198,12 +4198,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>3495717</t>
+          <t>3496666</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>3520859</t>
+          <t>3521037</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -4213,12 +4213,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>98,62%</t>
+          <t>98,65%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>99,33%</t>
+          <t>99,34%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -4233,12 +4233,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>6871038</t>
+          <t>6872187</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>6901733</t>
+          <t>6902057</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -4248,12 +4248,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>99,02%</t>
+          <t>99,04%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>99,46%</t>
+          <t>99,47%</t>
         </is>
       </c>
     </row>
